--- a/code/2/output/Q2_结果.xlsx
+++ b/code/2/output/Q2_结果.xlsx
@@ -1303,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col width="12" customWidth="1" style="3" min="1" max="2"/>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1653.854</v>
+        <v>1727.319</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.952542</v>
+        <v>1.905101</v>
       </c>
     </row>
     <row r="3">
@@ -1420,14 +1420,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1612.025</v>
+        <v>2007.733</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.957748</v>
+        <v>3.028173</v>
       </c>
     </row>
     <row r="4">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BAT-A03</t>
+          <t>BAT-B01</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1456,14 +1456,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S001→S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1906.847</v>
+        <v>1923.801</v>
       </c>
       <c r="H4" t="n">
-        <v>2.315093</v>
+        <v>2.755238</v>
       </c>
     </row>
     <row r="5">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAT-A04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1492,14 +1492,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1163.536</v>
+        <v>1868.598</v>
       </c>
       <c r="H5" t="n">
-        <v>1.135924</v>
+        <v>2.137307</v>
       </c>
     </row>
     <row r="6">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BAT-B01</t>
+          <t>BAT-C01</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1923.801</v>
+        <v>2111.008</v>
       </c>
       <c r="H6" t="n">
-        <v>2.755238</v>
+        <v>5.871638</v>
       </c>
     </row>
     <row r="7">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BAT-B02</t>
+          <t>BAT-C02</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1564,14 +1564,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1808.598</v>
+        <v>1627.427</v>
       </c>
       <c r="H7" t="n">
-        <v>1.922258</v>
+        <v>2.728484</v>
       </c>
     </row>
     <row r="8">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1592,22 +1592,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BAT-C01</t>
+          <t>BAT-C03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1627.427</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006→S007</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2111.008</v>
+        <v>4107.206</v>
       </c>
       <c r="H8" t="n">
-        <v>6.300757</v>
+        <v>4.305306</v>
       </c>
     </row>
     <row r="9">
@@ -1618,32 +1618,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BAT-C02</t>
+          <t>BAT-B03</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1868.598</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S001→S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2256.904</v>
+        <v>3423.171</v>
       </c>
       <c r="H9" t="n">
-        <v>4.147999</v>
+        <v>1.821047</v>
       </c>
     </row>
     <row r="10">
@@ -1654,32 +1654,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAT-A05</t>
+          <t>BAT-B04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1163.536</v>
+        <v>1923.801</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S010→S014</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3418.068</v>
+        <v>3434.202</v>
       </c>
       <c r="H10" t="n">
-        <v>2.479566</v>
+        <v>1.824569</v>
       </c>
     </row>
     <row r="11">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAT-B03</t>
+          <t>BAT-C04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1808.598</v>
+        <v>2111.008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3444.789</v>
+        <v>3606.435</v>
       </c>
       <c r="H11" t="n">
-        <v>1.779798</v>
+        <v>2.926273</v>
       </c>
     </row>
     <row r="12">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAT-B04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1923.801</v>
+        <v>3461.431</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3499.992</v>
+        <v>5447.204</v>
       </c>
       <c r="H12" t="n">
-        <v>1.656286</v>
+        <v>2.882269</v>
       </c>
     </row>
     <row r="13">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAT-C03</t>
+          <t>BAT-C02</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2111.008</v>
+        <v>3606.435</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007→S003</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3671.872</v>
+        <v>6299.749</v>
       </c>
       <c r="H13" t="n">
-        <v>2.593979</v>
+        <v>6.081514</v>
       </c>
     </row>
     <row r="14">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BAT-C04</t>
+          <t>BAT-B01</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2256.904</v>
+        <v>3784.404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3752.331</v>
+        <v>5804.647</v>
       </c>
       <c r="H14" t="n">
-        <v>2.821078</v>
+        <v>2.935637</v>
       </c>
     </row>
     <row r="15">
@@ -1834,21 +1834,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BAT-B02</t>
+          <t>BAT-C01</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3444.789</v>
+        <v>4534.577</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5668.58</v>
+        <v>7113.118</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96122</v>
+        <v>6.382961</v>
       </c>
     </row>
     <row r="16">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1880,22 +1880,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BAT-B01</t>
+          <t>BAT-B03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3784.404</v>
+        <v>5447.204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S005→S008</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5948.195</v>
+        <v>7276.778</v>
       </c>
       <c r="H16" t="n">
-        <v>3.043673</v>
+        <v>2.310906</v>
       </c>
     </row>
     <row r="17">
@@ -1906,32 +1906,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BAT-C02</t>
+          <t>BAT-B04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4213.654</v>
+        <v>5804.647</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001→S005</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6649.465</v>
+        <v>7637.9</v>
       </c>
       <c r="H17" t="n">
-        <v>5.991169</v>
+        <v>2.042764</v>
       </c>
     </row>
     <row r="18">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1952,22 +1952,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BAT-C01</t>
+          <t>BAT-C04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4650.796</v>
+        <v>6299.749</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005→S004</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6955.982</v>
+        <v>8885.540000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>6.176919</v>
+        <v>6.119611</v>
       </c>
     </row>
     <row r="19">
@@ -1978,32 +1978,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BAT-B03</t>
+          <t>BAT-C03</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5668.58</v>
+        <v>7113.118</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7498.154</v>
+        <v>8760.023999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.310906</v>
+        <v>3.78066</v>
       </c>
     </row>
     <row r="20">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2024,130 +2024,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAT-B04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5948.195</v>
+        <v>7362.854</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S001→S009</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7724.285</v>
+        <v>8552.485000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>1.983189</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BAT-C03</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6649.465</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S011→S005→S008</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>9657.611999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6.262018</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Q2T021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U08</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BAT-C04</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6955.982</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>9127.793</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.836361</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q2T022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BAT-B02</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>7618.442</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>9378.332</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.368652</v>
+        <v>1.077173</v>
       </c>
     </row>
   </sheetData>
@@ -2200,7 +2092,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Q2T003</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -2209,7 +2101,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>879.359</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="3">
@@ -2220,7 +2112,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2229,7 +2121,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1278.898</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="4">
@@ -2240,7 +2132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T016</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2249,7 +2141,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1278.898</v>
+        <v>6662.95</v>
       </c>
     </row>
     <row r="5">
@@ -2260,7 +2152,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2269,7 +2161,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1278.898</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="6">
@@ -2280,7 +2172,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2289,7 +2181,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1278.898</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="7">
@@ -2300,7 +2192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2309,7 +2201,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3439.802</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="8">
@@ -2320,7 +2212,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2329,7 +2221,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1278.898</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="9">
@@ -2340,7 +2232,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2349,7 +2241,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3439.802</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="10">
@@ -2360,7 +2252,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2369,7 +2261,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1278.898</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="11">
@@ -2380,7 +2272,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q2T019</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2389,7 +2281,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6806.497</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="12">
@@ -2400,7 +2292,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2409,7 +2301,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3439.802</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="13">
@@ -2420,7 +2312,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2429,7 +2321,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3439.802</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="14">
@@ -2440,7 +2332,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2449,7 +2341,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1278.898</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="15">
@@ -2460,7 +2352,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2469,7 +2361,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3439.802</v>
+        <v>1314.898</v>
       </c>
     </row>
     <row r="16">
@@ -2480,7 +2372,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2489,7 +2381,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3439.802</v>
+        <v>3293.906</v>
       </c>
     </row>
     <row r="17">
@@ -2500,7 +2392,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2T022</t>
+          <t>Q2T002</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2509,7 +2401,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8780.326999999999</v>
+        <v>1285.806</v>
       </c>
     </row>
     <row r="18">
@@ -2520,7 +2412,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2540,7 +2432,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2T022</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2549,7 +2441,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8780.326999999999</v>
+        <v>1488.914</v>
       </c>
     </row>
     <row r="20">
@@ -2560,7 +2452,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2580,7 +2472,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2600,7 +2492,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T002</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2609,7 +2501,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1488.914</v>
+        <v>1285.806</v>
       </c>
     </row>
     <row r="23">
@@ -2620,7 +2512,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2640,7 +2532,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q2T007</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2660,7 +2552,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2669,7 +2561,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5859.019</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="26">
@@ -2680,7 +2572,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2689,7 +2581,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5859.019</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="27">
@@ -2700,7 +2592,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2T021</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2709,7 +2601,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8337.347</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="28">
@@ -2720,7 +2612,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2729,7 +2621,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5859.019</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="29">
@@ -2740,7 +2632,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T013</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2749,7 +2641,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5859.019</v>
+        <v>5072.499</v>
       </c>
     </row>
     <row r="30">
@@ -2760,7 +2652,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2769,7 +2661,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5859.019</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="31">
@@ -2780,7 +2672,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2T021</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2789,7 +2681,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8337.347</v>
+        <v>5509.304</v>
       </c>
     </row>
     <row r="32">
@@ -2800,7 +2692,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T013</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2809,7 +2701,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5859.019</v>
+        <v>5072.499</v>
       </c>
     </row>
     <row r="33">
@@ -2820,7 +2712,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q2T017</t>
+          <t>Q2T011</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2829,7 +2721,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6236.359</v>
+        <v>4765.964</v>
       </c>
     </row>
     <row r="34">
@@ -2849,7 +2741,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6236.359</v>
+        <v>8165.917</v>
       </c>
     </row>
     <row r="35">
@@ -2860,7 +2752,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Q2T017</t>
+          <t>Q2T011</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2869,7 +2761,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6236.359</v>
+        <v>4765.964</v>
       </c>
     </row>
     <row r="36">
@@ -2880,7 +2772,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q2T017</t>
+          <t>Q2T011</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2889,7 +2781,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6236.359</v>
+        <v>4765.964</v>
       </c>
     </row>
     <row r="37">
@@ -2909,7 +2801,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6236.359</v>
+        <v>8165.917</v>
       </c>
     </row>
     <row r="38">
@@ -2929,7 +2821,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6236.359</v>
+        <v>8165.917</v>
       </c>
     </row>
     <row r="39">
@@ -2940,7 +2832,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q2T014</t>
+          <t>Q2T017</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2949,7 +2841,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4487.059</v>
+        <v>7566.407</v>
       </c>
     </row>
     <row r="40">
@@ -2960,7 +2852,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T017</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2969,7 +2861,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8381.727999999999</v>
+        <v>7566.407</v>
       </c>
     </row>
     <row r="41">
@@ -2980,7 +2872,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T016</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2881,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8381.727999999999</v>
+        <v>7161.144</v>
       </c>
     </row>
     <row r="42">
@@ -3000,7 +2892,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T017</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3009,7 +2901,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8381.727999999999</v>
+        <v>7566.407</v>
       </c>
     </row>
     <row r="43">
@@ -3020,7 +2912,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q2T015</t>
+          <t>Q2T016</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3029,7 +2921,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4796.674</v>
+        <v>7161.144</v>
       </c>
     </row>
     <row r="44">
@@ -3040,7 +2932,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T014</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3049,7 +2941,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8381.727999999999</v>
+        <v>5729.235</v>
       </c>
     </row>
     <row r="45">
@@ -3060,7 +2952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3069,7 +2961,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="46">
@@ -3080,7 +2972,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3089,7 +2981,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="47">
@@ -3100,7 +2992,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3109,7 +3001,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="48">
@@ -3120,7 +3012,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3129,7 +3021,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="49">
@@ -3140,7 +3032,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3149,7 +3041,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="50">
@@ -3160,7 +3052,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3169,7 +3061,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3320.085</v>
+        <v>2896.504</v>
       </c>
     </row>
     <row r="51">
@@ -3180,7 +3072,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q2T010</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3189,7 +3081,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2934.334</v>
+        <v>3547.425</v>
       </c>
     </row>
     <row r="52">
@@ -3200,7 +3092,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q2T011</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3209,7 +3101,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2989.537</v>
+        <v>3547.425</v>
       </c>
     </row>
     <row r="53">
@@ -3220,7 +3112,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q2T010</t>
+          <t>Q2T001</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3229,7 +3121,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2934.334</v>
+        <v>1141.299</v>
       </c>
     </row>
     <row r="54">
@@ -3240,7 +3132,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q2T011</t>
+          <t>Q2T001</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3249,7 +3141,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2989.537</v>
+        <v>1141.299</v>
       </c>
     </row>
     <row r="55">
@@ -3260,7 +3152,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q2T010</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3269,7 +3161,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2934.334</v>
+        <v>4870.136</v>
       </c>
     </row>
     <row r="56">
@@ -3280,7 +3172,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T014</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3289,7 +3181,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8953.572</v>
+        <v>6409.078</v>
       </c>
     </row>
     <row r="57">
@@ -3300,7 +3192,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T014</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3309,7 +3201,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8953.572</v>
+        <v>6409.078</v>
       </c>
     </row>
     <row r="58">
@@ -3329,7 +3221,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4995.861</v>
+        <v>6409.078</v>
       </c>
     </row>
     <row r="59">
@@ -3340,7 +3232,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q2T015</t>
+          <t>Q2T014</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3349,7 +3241,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5275.476</v>
+        <v>6409.078</v>
       </c>
     </row>
     <row r="60">
@@ -3369,7 +3261,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4995.861</v>
+        <v>6409.078</v>
       </c>
     </row>
     <row r="61">
@@ -3380,7 +3272,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q2T019</t>
+          <t>Q2T018</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3389,7 +3281,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7255.485</v>
+        <v>8270.456</v>
       </c>
     </row>
     <row r="62">
@@ -3400,7 +3292,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q2T019</t>
+          <t>Q2T018</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3409,7 +3301,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7255.485</v>
+        <v>8270.456</v>
       </c>
     </row>
     <row r="63">
@@ -3420,7 +3312,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2T003</t>
+          <t>Q2T018</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3429,7 +3321,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1342.669</v>
+        <v>8270.456</v>
       </c>
     </row>
     <row r="64">
@@ -3440,7 +3332,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2T009</t>
+          <t>Q2T008</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3449,7 +3341,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2237.999</v>
+        <v>2953.421</v>
       </c>
     </row>
     <row r="65">
@@ -3460,7 +3352,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q2T001</t>
+          <t>Q2T008</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3469,7 +3361,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1104.463</v>
+        <v>2953.421</v>
       </c>
     </row>
     <row r="66">
@@ -3480,7 +3372,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2T001</t>
+          <t>Q2T008</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3489,7 +3381,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1104.463</v>
+        <v>2953.421</v>
       </c>
     </row>
     <row r="67">
@@ -3500,7 +3392,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T019</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3509,7 +3401,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7737.97</v>
+        <v>8269.856</v>
       </c>
     </row>
     <row r="68">
@@ -3520,7 +3412,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2T020</t>
+          <t>Q2T019</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3529,7 +3421,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7737.97</v>
+        <v>8269.856</v>
       </c>
     </row>
     <row r="69">
@@ -3540,7 +3432,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2T004</t>
+          <t>Q2T019</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3549,7 +3441,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>833.955</v>
+        <v>8269.856</v>
       </c>
     </row>
     <row r="70">
@@ -3560,7 +3452,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2T005</t>
+          <t>Q2T003</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3580,7 +3472,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q2T005</t>
+          <t>Q2T003</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3600,7 +3492,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q2T005</t>
+          <t>Q2T003</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3620,7 +3512,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T009</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3629,7 +3521,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1778.923</v>
+        <v>2986.535</v>
       </c>
     </row>
     <row r="74">
@@ -3640,7 +3532,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q2T002</t>
+          <t>Q2T009</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3649,7 +3541,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1083.546</v>
+        <v>2986.535</v>
       </c>
     </row>
     <row r="75">
@@ -3660,7 +3552,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q2T002</t>
+          <t>Q2T009</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3669,7 +3561,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1083.546</v>
+        <v>2986.535</v>
       </c>
     </row>
     <row r="76">
@@ -3680,7 +3572,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2T009</t>
+          <t>Q2T004</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3689,7 +3581,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2701.143</v>
+        <v>1241.856</v>
       </c>
     </row>
     <row r="77">
@@ -3700,7 +3592,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q2T006</t>
+          <t>Q2T004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3709,7 +3601,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1181.856</v>
+        <v>1241.856</v>
       </c>
     </row>
     <row r="78">
@@ -3720,7 +3612,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q2T006</t>
+          <t>Q2T004</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3729,7 +3621,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1181.856</v>
+        <v>1241.856</v>
       </c>
     </row>
     <row r="79">
@@ -3740,7 +3632,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q2T018</t>
+          <t>Q2T015</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3749,7 +3641,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6886.807</v>
+        <v>6665.431</v>
       </c>
     </row>
     <row r="80">
@@ -3760,7 +3652,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q2T018</t>
+          <t>Q2T015</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3769,7 +3661,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6886.807</v>
+        <v>6665.431</v>
       </c>
     </row>
     <row r="81">
@@ -3780,7 +3672,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q2T018</t>
+          <t>Q2T015</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3789,7 +3681,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6886.807</v>
+        <v>6665.431</v>
       </c>
     </row>
   </sheetData>
